--- a/Final_Project/Traceability__Matrix.xlsx
+++ b/Final_Project/Traceability__Matrix.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="86">
   <si>
     <t>Test Case ID</t>
   </si>
@@ -279,6 +279,12 @@
   </si>
   <si>
     <t>Assignments are sorted correctly based on selected criteria.</t>
+  </si>
+  <si>
+    <t>TC-11</t>
+  </si>
+  <si>
+    <t>Register and Login</t>
   </si>
 </sst>
 </file>
@@ -666,7 +672,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="15">
     <border>
       <left/>
       <right/>
@@ -707,6 +713,47 @@
     <border>
       <left style="thin">
         <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
       </left>
       <right style="thin">
         <color auto="1"/>
@@ -841,7 +888,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -853,34 +900,34 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -965,7 +1012,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -978,6 +1025,14 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1324,7 +1379,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L11"/>
+  <dimension ref="A1:L12"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
@@ -1703,37 +1758,55 @@
       <c r="A11" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B11" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="C11" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="D11" s="3" t="s">
+      <c r="D11" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="E11" s="3" t="s">
+      <c r="E11" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="F11" s="3" t="s">
+      <c r="F11" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="G11" s="3" t="s">
+      <c r="G11" s="6" t="s">
         <v>83</v>
       </c>
-      <c r="H11" s="3" t="s">
+      <c r="H11" s="6" t="s">
         <v>83</v>
       </c>
-      <c r="I11" s="3" t="s">
+      <c r="I11" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="J11" s="3" t="s">
+      <c r="J11" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="K11" s="3" t="s">
+      <c r="K11" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="L11" s="5"/>
+      <c r="L11" s="7"/>
+    </row>
+    <row r="12" ht="48" customHeight="1" spans="1:12">
+      <c r="A12" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="B12" s="5"/>
+      <c r="C12" s="8"/>
+      <c r="D12" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="E12" s="8"/>
+      <c r="F12" s="8"/>
+      <c r="G12" s="8"/>
+      <c r="H12" s="8"/>
+      <c r="I12" s="8"/>
+      <c r="J12" s="8"/>
+      <c r="K12" s="8"/>
+      <c r="L12" s="8"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Final_Project/Traceability__Matrix.xlsx
+++ b/Final_Project/Traceability__Matrix.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="21000" windowHeight="9900"/>
+    <workbookView windowWidth="21216" windowHeight="10464"/>
   </bookViews>
   <sheets>
     <sheet name="Traceability Matrix" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="91">
   <si>
     <t>Test Case ID</t>
   </si>
@@ -95,6 +95,9 @@
     <t/>
   </si>
   <si>
+    <t>Ziran</t>
+  </si>
+  <si>
     <t>TC-02</t>
   </si>
   <si>
@@ -275,7 +278,8 @@
     <t>Sort assignments by due date and priority</t>
   </si>
   <si>
-    <t>Assignments with different due dates and priorities</t>
+    <t xml:space="preserve">Assignments with different due dates and priorities
+</t>
   </si>
   <si>
     <t>Assignments are sorted correctly based on selected criteria.</t>
@@ -285,6 +289,18 @@
   </si>
   <si>
     <t>Register and Login</t>
+  </si>
+  <si>
+    <t>Register and Login succeful</t>
+  </si>
+  <si>
+    <t>Username and Passwoed</t>
+  </si>
+  <si>
+    <t>Database save username and password for next login</t>
+  </si>
+  <si>
+    <t>Database save username and password for next login, use repeat username to register will report error1, can logout successful</t>
   </si>
 </sst>
 </file>
@@ -297,7 +313,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -321,13 +337,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
@@ -672,7 +681,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="15">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -715,38 +724,10 @@
         <color rgb="FF000000"/>
       </left>
       <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
         <color rgb="FF000000"/>
       </right>
       <top style="thin">
         <color rgb="FF000000"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
       </top>
       <bottom/>
       <diagonal/>
@@ -867,152 +848,152 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1023,16 +1004,25 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1466,32 +1456,34 @@
       <c r="K2" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="L2" s="4"/>
+      <c r="L2" s="4" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="3" ht="45" customHeight="1" spans="1:12">
       <c r="A3" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I3" s="3" t="s">
         <v>19</v>
@@ -1502,32 +1494,34 @@
       <c r="K3" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="L3" s="5"/>
+      <c r="L3" s="4" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="4" ht="45" customHeight="1" spans="1:12">
       <c r="A4" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="I4" s="3" t="s">
         <v>19</v>
@@ -1538,32 +1532,34 @@
       <c r="K4" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="L4" s="5"/>
+      <c r="L4" s="4" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="5" ht="45" customHeight="1" spans="1:12">
       <c r="A5" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="I5" s="3" t="s">
         <v>19</v>
@@ -1574,32 +1570,34 @@
       <c r="K5" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="L5" s="5"/>
+      <c r="L5" s="4" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="6" ht="45" customHeight="1" spans="1:12">
       <c r="A6" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="I6" s="3" t="s">
         <v>19</v>
@@ -1610,29 +1608,31 @@
       <c r="K6" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="L6" s="5"/>
+      <c r="L6" s="4" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="7" ht="45" customHeight="1" spans="1:12">
       <c r="A7" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H7" s="3"/>
       <c r="I7" s="3" t="s">
@@ -1644,32 +1644,34 @@
       <c r="K7" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="L7" s="5"/>
+      <c r="L7" s="4" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="8" ht="45" customHeight="1" spans="1:12">
       <c r="A8" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="I8" s="3" t="s">
         <v>19</v>
@@ -1680,32 +1682,34 @@
       <c r="K8" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="L8" s="5"/>
+      <c r="L8" s="4" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="9" ht="45" customHeight="1" spans="1:12">
       <c r="A9" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="I9" s="3" t="s">
         <v>19</v>
@@ -1716,32 +1720,34 @@
       <c r="K9" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="L9" s="5"/>
+      <c r="L9" s="4" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="10" ht="45" customHeight="1" spans="1:12">
       <c r="A10" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I10" s="3" t="s">
         <v>19</v>
@@ -1752,61 +1758,83 @@
       <c r="K10" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="L10" s="5"/>
+      <c r="L10" s="4" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="11" ht="45" customHeight="1" spans="1:12">
       <c r="A11" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="B11" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="C11" s="6" t="s">
+      <c r="B11" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="D11" s="6" t="s">
+      <c r="C11" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="E11" s="6" t="s">
+      <c r="D11" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="F11" s="6" t="s">
+      <c r="E11" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="G11" s="6" t="s">
+      <c r="F11" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="H11" s="6" t="s">
-        <v>83</v>
-      </c>
-      <c r="I11" s="6" t="s">
+      <c r="G11" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="H11" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="I11" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="J11" s="6" t="s">
+      <c r="J11" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="K11" s="6" t="s">
+      <c r="K11" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="L11" s="7"/>
+      <c r="L11" s="4" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="12" ht="48" customHeight="1" spans="1:12">
       <c r="A12" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="B12" s="5"/>
-      <c r="C12" s="8"/>
-      <c r="D12" s="9" t="s">
         <v>85</v>
       </c>
-      <c r="E12" s="8"/>
-      <c r="F12" s="8"/>
-      <c r="G12" s="8"/>
-      <c r="H12" s="8"/>
-      <c r="I12" s="8"/>
-      <c r="J12" s="8"/>
-      <c r="K12" s="8"/>
-      <c r="L12" s="8"/>
+      <c r="B12" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="E12" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="F12" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="G12" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="H12" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="I12" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="J12" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="K12" s="10"/>
+      <c r="L12" s="4" t="s">
+        <v>22</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Final_Project/Traceability__Matrix.xlsx
+++ b/Final_Project/Traceability__Matrix.xlsx
@@ -313,7 +313,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -325,16 +325,20 @@
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
+      <name val="Times New Roman"/>
       <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
-      <name val="宋体"/>
+      <name val="Times New Roman"/>
       <charset val="134"/>
-      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <charset val="134"/>
     </font>
     <font>
       <u/>
@@ -863,137 +867,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1001,28 +1005,31 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1384,7 +1391,7 @@
     <col min="11" max="11" width="25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28.8" spans="1:12">
+    <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1634,7 +1641,7 @@
       <c r="G7" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="H7" s="3"/>
+      <c r="H7" s="5"/>
       <c r="I7" s="3" t="s">
         <v>21</v>
       </c>
@@ -1766,34 +1773,34 @@
       <c r="A11" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="C11" s="5" t="s">
+      <c r="C11" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="D11" s="5" t="s">
+      <c r="D11" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="E11" s="5" t="s">
+      <c r="E11" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="F11" s="5" t="s">
+      <c r="F11" s="6" t="s">
         <v>83</v>
       </c>
-      <c r="G11" s="5" t="s">
+      <c r="G11" s="6" t="s">
         <v>84</v>
       </c>
-      <c r="H11" s="5" t="s">
+      <c r="H11" s="6" t="s">
         <v>84</v>
       </c>
-      <c r="I11" s="5" t="s">
+      <c r="I11" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="J11" s="5" t="s">
+      <c r="J11" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="K11" s="5" t="s">
+      <c r="K11" s="6" t="s">
         <v>21</v>
       </c>
       <c r="L11" s="4" t="s">
@@ -1810,28 +1817,28 @@
       <c r="C12" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="D12" s="6" t="s">
+      <c r="D12" s="7" t="s">
         <v>86</v>
       </c>
-      <c r="E12" s="6" t="s">
+      <c r="E12" s="7" t="s">
         <v>87</v>
       </c>
-      <c r="F12" s="7" t="s">
+      <c r="F12" s="8" t="s">
         <v>88</v>
       </c>
-      <c r="G12" s="7" t="s">
+      <c r="G12" s="8" t="s">
         <v>89</v>
       </c>
-      <c r="H12" s="8" t="s">
+      <c r="H12" s="9" t="s">
         <v>90</v>
       </c>
-      <c r="I12" s="9" t="s">
+      <c r="I12" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="J12" s="9" t="s">
+      <c r="J12" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="K12" s="10"/>
+      <c r="K12" s="11"/>
       <c r="L12" s="4" t="s">
         <v>22</v>
       </c>
